--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -6744,7 +6744,7 @@
         <v>57</v>
       </c>
       <c r="AD2" t="n">
-        <v>7123</v>
+        <v>7109</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -13524,7 +13524,7 @@
       <c r="AB93" t="s"/>
       <c r="AC93" t="s"/>
       <c r="AD93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:30">
@@ -13596,7 +13596,7 @@
       <c r="AB94" t="s"/>
       <c r="AC94" t="s"/>
       <c r="AD94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:30">
@@ -13666,7 +13666,7 @@
       <c r="AB95" t="s"/>
       <c r="AC95" t="s"/>
       <c r="AD95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:30">
@@ -13882,7 +13882,7 @@
       <c r="AB98" t="s"/>
       <c r="AC98" t="s"/>
       <c r="AD98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:30">
@@ -13954,7 +13954,7 @@
       <c r="AB99" t="s"/>
       <c r="AC99" t="s"/>
       <c r="AD99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:30">
@@ -14026,7 +14026,7 @@
       <c r="AB100" t="s"/>
       <c r="AC100" t="s"/>
       <c r="AD100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:30">
@@ -14098,7 +14098,7 @@
       <c r="AB101" t="s"/>
       <c r="AC101" t="s"/>
       <c r="AD101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:30">

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2129">
   <si>
     <t>資料名</t>
   </si>
@@ -6243,6 +6243,165 @@
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a3954326-8d89-5ff8-678e-341f60a907c6/manifest</t>
+  </si>
+  <si>
+    <t>極東熱帶醫學會第六囘總會役員名簿(ABC順)</t>
+  </si>
+  <si>
+    <t>キョクトウ ネッタイ イガクカイ ダイロッカイ ソウカイ ヤクイン メイボ ABCジュン</t>
+  </si>
+  <si>
+    <t>第六回極東熱帯医学会資料</t>
+  </si>
+  <si>
+    <t>jpn</t>
+  </si>
+  <si>
+    <t>図書</t>
+  </si>
+  <si>
+    <t>極東熱帶醫學會</t>
+  </si>
+  <si>
+    <t>キョクトウ ネッタイ イガクカイ</t>
+  </si>
+  <si>
+    <t>1925</t>
+  </si>
+  <si>
+    <t>41p ; 19cm</t>
+  </si>
+  <si>
+    <t>請求記号: 三宅:557|資料解説: 三宅文庫は三宅艮斎 ・ 秀 ・ 鑛一 ・ 仁の四代にわたる医家の蔵書図書。三宅秀(みやけひいず, 1848-1938)は東京大学医学部教授(病理学)、医学部長を務めた。役員名簿にも顧問として名が掲載されている。</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/684f0490-22da-124e-8922-569413b24c6a.json</t>
+  </si>
+  <si>
+    <t>684f0490-22da-124e-8922-569413b24c6a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/684f0490-22da-124e-8922-569413b24c6a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/665ffe49da2b093e5b9f7915c99bd53018eef20b.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1181318</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/684f0490-22da-124e-8922-569413b24c6a/manifest</t>
+  </si>
+  <si>
+    <t>極東熱帶醫學會第六囘總會第一報</t>
+  </si>
+  <si>
+    <t>キョクトウ ネッタイ イガクカイ ダイロッカイ ソウカイ ダイイッポウ</t>
+  </si>
+  <si>
+    <t>19p ; 18cm</t>
+  </si>
+  <si>
+    <t>請求記号: 三宅:559|内容注記: ペン字による修正あり</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5b784b61-4387-32a1-76a2-f5a437b015a1.json</t>
+  </si>
+  <si>
+    <t>5b784b61-4387-32a1-76a2-f5a437b015a1</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/5b784b61-4387-32a1-76a2-f5a437b015a1</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1aaade3b16d058349b6a24399f78709ff38853a5.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1181317</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5b784b61-4387-32a1-76a2-f5a437b015a1/manifest</t>
+  </si>
+  <si>
+    <t>Guide to the 6th Congress of the Far Eastern Association of Tropical Medicine</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>Congress of the Far Eastern Association of Tropical Medicine</t>
+  </si>
+  <si>
+    <t>東京</t>
+  </si>
+  <si>
+    <t>67 p. ; 19 cm</t>
+  </si>
+  <si>
+    <t>請求記号: 三宅:593|画像注記: 巻末メモ10枚(未記入)のうち9枚はデジタル化省略。|附属資料: タイムスケジュール表:33.2×39cm, 会場図:39×60cm</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/656ca1ee-6d01-4f56-3b47-7cd7ab08358e.json</t>
+  </si>
+  <si>
+    <t>656ca1ee-6d01-4f56-3b47-7cd7ab08358e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/656ca1ee-6d01-4f56-3b47-7cd7ab08358e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f653da06e4f3d3b98ed3168f9c62c609fc8c762d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1181316</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/656ca1ee-6d01-4f56-3b47-7cd7ab08358e/manifest</t>
+  </si>
+  <si>
+    <t>Reports of the medical exhibition : VI Congress of the Far Eastern Association of Tropical Medicine, 1925</t>
+  </si>
+  <si>
+    <t>東京帝國大學傳染病研究所内第六回極東熱帶醫學會</t>
+  </si>
+  <si>
+    <t>1927</t>
+  </si>
+  <si>
+    <t>4, 20, 43, 58 p., [26] leaves of plates : ill. ; 25 cm</t>
+  </si>
+  <si>
+    <t>請求記号:旧病院:2340|資料解説: 第六回極東熱帯医学会の事務局があった東京帝国大学伝染病研究所は、現在の東京大学医科学研究所である。旧蔵資料が柏図書館に移管されている(請求記号:旧医科研::2905) また医学図書館所蔵呉秀三文庫に呉が担当した展示資料解説の抜き刷りがある(請求記号: 呉:A:219)</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/58d5db0a-5370-099d-5840-dccdc7d2942b.json</t>
+  </si>
+  <si>
+    <t>58d5db0a-5370-099d-5840-dccdc7d2942b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/58d5db0a-5370-099d-5840-dccdc7d2942b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3dee9c6e1abe8fa9942ad697e9c017b8378c3982.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1181315</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/58d5db0a-5370-099d-5840-dccdc7d2942b/manifest</t>
   </si>
 </sst>
 </file>
@@ -6578,7 +6737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG195"/>
+  <dimension ref="A1:AG199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:33">
@@ -6780,7 +6939,7 @@
         <v>63</v>
       </c>
       <c r="AG2" t="n">
-        <v>7109</v>
+        <v>7304</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -21572,6 +21731,332 @@
         <v>3</v>
       </c>
     </row>
+    <row r="196" spans="1:33">
+      <c r="A196" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B196" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C196" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D196" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E196" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F196" t="s">
+        <v>2081</v>
+      </c>
+      <c r="G196" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H196" t="s"/>
+      <c r="I196" t="s"/>
+      <c r="J196" t="s">
+        <v>2083</v>
+      </c>
+      <c r="K196" t="s">
+        <v>2083</v>
+      </c>
+      <c r="L196" t="s">
+        <v>2084</v>
+      </c>
+      <c r="M196" t="s">
+        <v>2085</v>
+      </c>
+      <c r="N196" t="s"/>
+      <c r="O196" t="s">
+        <v>2086</v>
+      </c>
+      <c r="P196" t="s">
+        <v>2087</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>74</v>
+      </c>
+      <c r="R196" t="s">
+        <v>2088</v>
+      </c>
+      <c r="S196" t="s">
+        <v>76</v>
+      </c>
+      <c r="T196" t="s">
+        <v>2089</v>
+      </c>
+      <c r="U196" t="s">
+        <v>2090</v>
+      </c>
+      <c r="V196" t="s">
+        <v>79</v>
+      </c>
+      <c r="W196" t="s">
+        <v>80</v>
+      </c>
+      <c r="X196" t="s"/>
+      <c r="Y196" t="s">
+        <v>2078</v>
+      </c>
+      <c r="Z196" t="s">
+        <v>2091</v>
+      </c>
+      <c r="AA196" t="s"/>
+      <c r="AB196" t="s">
+        <v>2092</v>
+      </c>
+      <c r="AC196" t="s"/>
+      <c r="AD196" t="s"/>
+      <c r="AE196" t="s"/>
+      <c r="AF196" t="s"/>
+      <c r="AG196" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" spans="1:33">
+      <c r="A197" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B197" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C197" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D197" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E197" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F197" t="s">
+        <v>2081</v>
+      </c>
+      <c r="G197" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H197" t="s"/>
+      <c r="I197" t="s"/>
+      <c r="J197" t="s">
+        <v>2083</v>
+      </c>
+      <c r="K197" t="s">
+        <v>2083</v>
+      </c>
+      <c r="L197" t="s">
+        <v>2095</v>
+      </c>
+      <c r="M197" t="s">
+        <v>2096</v>
+      </c>
+      <c r="N197" t="s"/>
+      <c r="O197" t="s">
+        <v>2097</v>
+      </c>
+      <c r="P197" t="s">
+        <v>2098</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>74</v>
+      </c>
+      <c r="R197" t="s">
+        <v>2099</v>
+      </c>
+      <c r="S197" t="s">
+        <v>76</v>
+      </c>
+      <c r="T197" t="s">
+        <v>2100</v>
+      </c>
+      <c r="U197" t="s">
+        <v>2101</v>
+      </c>
+      <c r="V197" t="s">
+        <v>79</v>
+      </c>
+      <c r="W197" t="s">
+        <v>80</v>
+      </c>
+      <c r="X197" t="s"/>
+      <c r="Y197" t="s">
+        <v>2078</v>
+      </c>
+      <c r="Z197" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AA197" t="s"/>
+      <c r="AB197" t="s">
+        <v>2103</v>
+      </c>
+      <c r="AC197" t="s"/>
+      <c r="AD197" t="s"/>
+      <c r="AE197" t="s"/>
+      <c r="AF197" t="s"/>
+      <c r="AG197" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" spans="1:33">
+      <c r="A198" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B198" t="s"/>
+      <c r="C198" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D198" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E198" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F198" t="s">
+        <v>2106</v>
+      </c>
+      <c r="G198" t="s"/>
+      <c r="H198" t="s"/>
+      <c r="I198" t="s">
+        <v>2107</v>
+      </c>
+      <c r="J198" t="s">
+        <v>2083</v>
+      </c>
+      <c r="K198" t="s">
+        <v>2083</v>
+      </c>
+      <c r="L198" t="s">
+        <v>2108</v>
+      </c>
+      <c r="M198" t="s">
+        <v>2109</v>
+      </c>
+      <c r="N198" t="s"/>
+      <c r="O198" t="s">
+        <v>2110</v>
+      </c>
+      <c r="P198" t="s">
+        <v>2111</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>74</v>
+      </c>
+      <c r="R198" t="s">
+        <v>2112</v>
+      </c>
+      <c r="S198" t="s">
+        <v>76</v>
+      </c>
+      <c r="T198" t="s">
+        <v>2113</v>
+      </c>
+      <c r="U198" t="s">
+        <v>2114</v>
+      </c>
+      <c r="V198" t="s">
+        <v>79</v>
+      </c>
+      <c r="W198" t="s"/>
+      <c r="X198" t="s"/>
+      <c r="Y198" t="s">
+        <v>2078</v>
+      </c>
+      <c r="Z198" t="s">
+        <v>2115</v>
+      </c>
+      <c r="AA198" t="s"/>
+      <c r="AB198" t="s">
+        <v>2116</v>
+      </c>
+      <c r="AC198" t="s"/>
+      <c r="AD198" t="s"/>
+      <c r="AE198" t="s"/>
+      <c r="AF198" t="s"/>
+      <c r="AG198" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="199" spans="1:33">
+      <c r="A199" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B199" t="s"/>
+      <c r="C199" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D199" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E199" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F199" t="s">
+        <v>2106</v>
+      </c>
+      <c r="G199" t="s"/>
+      <c r="H199" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I199" t="s">
+        <v>2107</v>
+      </c>
+      <c r="J199" t="s">
+        <v>2119</v>
+      </c>
+      <c r="K199" t="s">
+        <v>2119</v>
+      </c>
+      <c r="L199" t="s">
+        <v>2120</v>
+      </c>
+      <c r="M199" t="s">
+        <v>2121</v>
+      </c>
+      <c r="N199" t="s"/>
+      <c r="O199" t="s">
+        <v>2122</v>
+      </c>
+      <c r="P199" t="s">
+        <v>2123</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>74</v>
+      </c>
+      <c r="R199" t="s">
+        <v>2124</v>
+      </c>
+      <c r="S199" t="s">
+        <v>76</v>
+      </c>
+      <c r="T199" t="s">
+        <v>2125</v>
+      </c>
+      <c r="U199" t="s">
+        <v>2126</v>
+      </c>
+      <c r="V199" t="s">
+        <v>79</v>
+      </c>
+      <c r="W199" t="s"/>
+      <c r="X199" t="s"/>
+      <c r="Y199" t="s">
+        <v>2078</v>
+      </c>
+      <c r="Z199" t="s">
+        <v>2127</v>
+      </c>
+      <c r="AA199" t="s"/>
+      <c r="AB199" t="s">
+        <v>2128</v>
+      </c>
+      <c r="AC199" t="s"/>
+      <c r="AD199" t="s"/>
+      <c r="AE199" t="s"/>
+      <c r="AF199" t="s"/>
+      <c r="AG199" t="n">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -5597,7 +5597,7 @@
     <t>明治13年 (1880)</t>
   </si>
   <si>
-    <t>自明治十一年十二月 至同十二年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=30|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=90|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=91</t>
+    <t>自明治十一年十二月 至同十二年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=86|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=86|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=87|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=88</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bb90a597-3912-6cd7-2753-a5ca192b05f8.json</t>
@@ -5630,7 +5630,7 @@
     <t>明治14年 (1881)</t>
   </si>
   <si>
-    <t>自明治十二年十二月 至同十三年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=34|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=85|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=86|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=87</t>
+    <t>自明治十二年十二月 至同十三年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=34|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=83|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=85</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/14dc3dfd-621f-164d-1daf-304e0448360c.json</t>
@@ -6939,7 +6939,7 @@
         <v>63</v>
       </c>
       <c r="AG2" t="n">
-        <v>7304</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -20405,7 +20405,7 @@
       <c r="AE178" t="s"/>
       <c r="AF178" t="s"/>
       <c r="AG178" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="179" spans="1:33">
@@ -20480,7 +20480,7 @@
       <c r="AE179" t="s"/>
       <c r="AF179" t="s"/>
       <c r="AG179" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="180" spans="1:33">

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -6939,7 +6939,7 @@
         <v>63</v>
       </c>
       <c r="AG2" t="n">
-        <v>7299</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -13838,7 +13838,7 @@
       <c r="AE91" t="s"/>
       <c r="AF91" t="s"/>
       <c r="AG91" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:33">

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -9336,12 +9336,12 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>1926年以前</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>小キャビネ</t>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>解説: 掲載:  シーボルト先生が帰国の時、高良齋に與へし薬厨(高壯吉君藏)--『シーボルト先生 : 其生涯及功業』 第百九十九図|加工: マスキング|現秩序no.: 65|紙焼き記載no.: C41</t>
+          <t>解説: 掲載: シーボルト先生が帰国の時、高良齋に與へし薬厨(高壯吉君藏)--『シーボルト先生 : 其生涯及功業』 第百九十九図|加工: マスキング|現秩序no.: 65|紙焼き記載no.: C41</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/19c851d97555999d7e0bd0be22b621bfd1d657d0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a72d5843e862d1ae6141735255e5a84595c1aac9.jpg</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1380118</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1380272</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9394,11 +9394,7 @@
           <t>東京大学医学図書館 Medical Library, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr">
         <is>

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ミズタニ ホウブン シャセイ ハシドコロ ズ イトウ ケイスケ キジュツ ドウ ユライキ|Mizutani Hobun shasei hashidokoro zu Ito Keisuke kijutsu do yuraiki</t>
+          <t>ミズタニ ホウブン シャセイ ハシリドコロ ズ イトウ ケイスケ キジュツ ドウ ユライキ|Mizutani Hobun shasei hashidokoro zu Ito Keisuke kijutsu do yuraiki</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>請求記号: 呉 5|資料解説: 平戸嵐山家とは、平戸藩の藩医嵐山甫庵に始まる医家と推測されるが、解剖についての詳細は不明。印記:「呉氏文庫」|刊年2: 不明</t>
+          <t>請求記号: 呉 5|登録番号: M26315|資料解説: 平戸嵐山家とは、平戸藩の藩医嵐山甫庵に始まる医家と推測されるが、解剖についての詳細は不明。印記:「呉氏文庫」|刊年2: 不明</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>請求記号: 呉 5|資料解説: 平戸嵐山家とは、平戸藩の藩医嵐山甫庵に始まる医家と推測されるが、解剖についての詳細は不明。印記:「呉氏文庫」|刊年2: 不明</t>
+          <t>請求記号: 呉 5|登録番号: M26316|資料解説: 平戸嵐山家とは、平戸藩の藩医嵐山甫庵に始まる医家と推測されるが、解剖についての詳細は不明。印記:「呉氏文庫」|刊年2: 不明</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
@@ -25529,7 +25529,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>請求記号:呉 4|解説:曲直瀬道三、前野良沢など室町~江戸時代の医師や蘭学者らの書画54点を、呉自身で折帖に仕立てたもの。 表紙の「芳渓」はもっとも多く使われた呉の号である。</t>
+          <t>請求記号:呉 4|登録番号:M26314|解説:曲直瀬道三、前野良沢など室町~江戸時代の医師や蘭学者らの書画54点を、呉自身で折帖に仕立てたもの。 表紙の「芳渓」はもっとも多く使われた呉の号である。</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
@@ -28077,7 +28077,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>医聖堂前哲帖 22 作者不明</t>
+          <t>医聖堂前哲帖 22 [  栗本丹洲 ]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -28098,10 +28098,14 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>作者不明</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr"/>
+          <t>[ 栗本丹洲 ]</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>くりもと たんしゅう|Kurimoto Tanshu</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
@@ -28111,7 +28115,11 @@
           <t>26.7×20.4cm</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>江戸時代後期の医師、本草学者。幕府奥医師、4代目栗本瑞見。著作に「千虫譜」など。(1756-1834)</t>
+        </is>
+      </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
@@ -31727,7 +31735,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>解説:官立となった種痘所が、文久元年に発行した種痘接種を勧める告知文。 牛痘種痘渡来の由来や種痘所の歴史を述べ、種痘所への案内地図を掲載している。</t>
+          <t>解説:官立となった種痘所が、文久元年に発行した種痘接種を勧める告知文。 牛痘種痘渡来の由来や種痘所の歴史を述べ、種痘所への案内地図を掲載している。|原本所蔵: 順天堂大学</t>
         </is>
       </c>
       <c r="N262" t="inlineStr"/>
@@ -34049,7 +34057,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>自明治九年十二月 至同十年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=36|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=36|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=37|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=38|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=39|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=55</t>
+          <t>請求記号: 史料室:9008|自明治九年十二月 至同十年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=36|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=36|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=37|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=38|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=39|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/8a908d81-5ef0-3c30-5808-886df022821f#?cv=55</t>
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
@@ -34163,7 +34171,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>自明治十年十二月 至同十一年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=30|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=30|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=31|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=32</t>
+          <t>請求記号: 史料室:9008|自明治十年十二月 至同十一年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=30|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=30|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=31|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4c8506b1-8f77-39f3-2643-6bbc98ba8790#?cv=32</t>
         </is>
       </c>
       <c r="N284" t="inlineStr"/>
@@ -34277,7 +34285,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>自明治十一年十二月 至同十二年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=86|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=86|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=87|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=88</t>
+          <t>請求記号: 史料室:9008|自明治十一年十二月 至同十二年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=30|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=90|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/bb90a597-3912-6cd7-2753-a5ca192b05f8#?cv=91</t>
         </is>
       </c>
       <c r="N285" t="inlineStr"/>
@@ -34391,7 +34399,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>自明治十二年十二月 至同十三年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=34|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=83|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=85</t>
+          <t>請求記号: 史料室:9008|自明治十二年十二月 至同十三年十一月|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=6|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=34|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=83|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/14dc3dfd-621f-164d-1daf-304e0448360c#?cv=85</t>
         </is>
       </c>
       <c r="N286" t="inlineStr"/>
@@ -34509,7 +34517,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>医学校の明治元年から9年までの記録。|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=13|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=15|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=19|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=24|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=33|*白紙頁は撮影していない</t>
+          <t>請求記号: 史料室:9005|医学校の明治元年から9年までの記録。|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=13|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=15|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=19|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=24|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/2768e7c9-4dda-7169-5c21-51f9fb5d60f6#?cv=33|*白紙頁は撮影していない</t>
         </is>
       </c>
       <c r="N287" t="inlineStr"/>
@@ -34627,7 +34635,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=12|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=13|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=14|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=14|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=15|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=16|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=17|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=17|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=18|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=19|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=20|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=21|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=23|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=24|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=24|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=26|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=31|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=32|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=33|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=45</t>
+          <t>請求記号: 史料室:9007|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=12|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=13|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=14|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=14|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=15|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=16|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=17|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=17|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=18|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=19|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=20|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=21|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=23|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=24|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=24|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=26|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=31|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=32|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=33|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/de6aeb4d-9de6-6411-2d82-8821672c0bd5#?cv=45</t>
         </is>
       </c>
       <c r="N288" t="inlineStr"/>
@@ -34745,7 +34753,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=11|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=12|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=16|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=17|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=21|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=23|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=28|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=43|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=43|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=46|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=66|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=69|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=70|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=71|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=74|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=82|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=88|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=94|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=97|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=101|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=133|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=139|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=140|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=141|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=154</t>
+          <t>請求記号: 史料室:9007|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=5|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=11|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=12|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=16|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=17|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=21|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=23|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=28|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=43|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=43|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=46|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=66|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=69|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=70|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=71|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=74|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=82|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=88|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=94|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=97|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=101|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=133|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=139|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=140|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=141|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/eac90c10-0506-9f9b-0f22-f2460b201cc8#?cv=154</t>
         </is>
       </c>
       <c r="N289" t="inlineStr"/>
@@ -34863,7 +34871,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=25|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=26|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=45|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=46|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=46|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=53|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=56|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=57|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=62|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=67|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=69|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=74|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=80|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=114|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=118|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=128</t>
+          <t>請求記号: 史料室:9007|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=25|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=26|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=29|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=45|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=46|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=46|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=53|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=56|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=57|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=62|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=67|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=69|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=74|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=80|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=114|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=118|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4d6fe455-003d-2550-3e2b-4dab29dd504c#?cv=128</t>
         </is>
       </c>
       <c r="N290" t="inlineStr"/>
@@ -34981,7 +34989,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=25|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=26|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=28|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=47|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=48|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=48|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=55|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=58|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=59|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=60|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=63|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=65|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=72|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=75|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=96|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=101|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=114</t>
+          <t>請求記号: 史料室:9007|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=3|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=7|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=8|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=25|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=26|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=28|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=44|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=47|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=48|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=48|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=55|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=58|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=59|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=60|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=63|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=65|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=72|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=75|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=96|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=101|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/3a03bdb6-8007-6e53-8506-3dc544c93775#?cv=114</t>
         </is>
       </c>
       <c r="N291" t="inlineStr"/>
@@ -35099,7 +35107,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=11|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=18|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=54|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=55|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=60|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=73|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=73|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=75|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=76|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=77|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=87|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=92|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=99|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=103|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=123|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=130|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=141</t>
+          <t>請求記号: 史料室:9007|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=2|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=4|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=9|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=10|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=11|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=18|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=54|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=55|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=60|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=73|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=73|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=75|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=76|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=77|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=84|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=87|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=89|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=92|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=99|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=103|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=123|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=130|https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/4ce5a99d-6d90-12dd-36a4-e5176deb6137#?cv=141</t>
         </is>
       </c>
       <c r="N292" t="inlineStr"/>
@@ -35217,7 +35225,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>請求記号: 呉 6|資料解説: 「精神病学随抄」と記された短冊付き。「辟邪絵毘沙門天像」「弘法大師行伏絵詞」「病之草子」等の模写、抜写。</t>
+          <t>請求記号: 呉 6|登録番号: M26317|資料解説: 「精神病学随抄」と記された短冊付き。「辟邪絵毘沙門天像」「弘法大師行伏絵詞」「病之草子」等の模写、抜写。</t>
         </is>
       </c>
       <c r="N293" t="inlineStr"/>
@@ -35335,7 +35343,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>請求記号: 呉 7|資料解説: 外題「三十二御懇報翠竹院書」、箱書「道三文春」「曲直瀬道三先生文」、 極書あり。呉6「精神病学随抄」の短冊の欠損部分が箱に同封されていた。</t>
+          <t>請求記号: 呉 7|登録番号: M26323|資料解説: 外題「三十二御懇報翠竹院書」、箱書「道三文春」「曲直瀬道三先生文」、 極書あり。呉6「精神病学随抄」の短冊の欠損部分が箱に同封されていた。</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -35461,7 +35469,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>請求記号: 呉 9|資料解説: 外題「新宮凉庭先生」、本文「竹門迎客禮無遺 錦軸銅髯亦更奇 佳趣那辺人若問 清茶一椀酒醒時 辛卯臘尾題山中氏茶室 涼亭山人」 、落款「新宮碩」「涼亭」、 外書に「呉氏所蔵」とあり。</t>
+          <t>請求記号: 呉 9|登録番号: M26322|資料解説: 外題「新宮凉庭先生」、本文「竹門迎客禮無遺 錦軸銅髯亦更奇 佳趣那辺人若問 清茶一椀酒醒時 辛卯臘尾題山中氏茶室 涼亭山人」 、落款「新宮碩」「涼亭」、 外書に「呉氏所蔵」とあり。</t>
         </is>
       </c>
       <c r="N295" t="inlineStr"/>
@@ -35579,7 +35587,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>請求記号: 呉 10|資料解説:本文「出市嵐山己入望 雅衣小幌歩斜陽 春初摘翠西郊路 野菜花開井々黄 録近製 檉翁」、外書に「呉氏翠微庵」とあり。</t>
+          <t>請求記号: 呉 10|登録番号: M26324|資料解説:本文「出市嵐山己入望 雅衣小幌歩斜陽 春初摘翠西郊路 野菜花開井々黄 録近製 檉翁」、外書に「呉氏翠微庵」とあり。</t>
         </is>
       </c>
       <c r="N296" t="inlineStr"/>
@@ -35701,7 +35709,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>請求記号: 呉 11|資料解説: 外題「多紀茝庭」、本文「問居驚物候 忽己動微涼 無限雲泉意 蝉声備名陽 丁亥夏日 茝庭拙者写題」、落款 「劉元堅」「茝庭」。</t>
+          <t>請求記号: 呉 11|登録番号: M26326|資料解説: 外題「多紀茝庭」、本文「問居驚物候 忽己動微涼 無限雲泉意 蝉声備名陽 丁亥夏日 茝庭拙者写題」、落款 「劉元堅」「茝庭」。</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -35823,7 +35831,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>請求記号: 呉 12|資料解説: 外題「多紀先生二行」、本文「方不在多 心契則靈 症不在難 意會則明 丹波元堅書」、落款「奚暇斎□(房)」「多紀元堅」「茝庭」、 表装に朱印「呉氏蔵書之印」。</t>
+          <t>請求記号: 呉 12|登録番号: M26321|資料解説: 外題「多紀先生二行」、本文「方不在多 心契則靈 症不在難 意會則明 丹波元堅書」、落款「奚暇斎□(房)」「多紀元堅」「茝庭」、 表装に朱印「呉氏蔵書之印」。</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -35945,7 +35953,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>請求記号: 呉 13|資料解説: 本文「韙哉長沙太守感淪喪 傷横夭力論傷寒之理 遂垂衆方之妙何啻見 病知源医家萬世師表 丹波元簡拜贊 男元堅謹書」、 落款「毉元堅」「赤柔」「千春之印」「融斎」。</t>
+          <t>請求記号: 呉 13|登録番号: M26319|資料解説: 本文「韙哉長沙太守感淪喪 傷横夭力論傷寒之理 遂垂衆方之妙何啻見 病知源医家萬世師表 丹波元簡拜贊 男元堅謹書」、 落款「毉元堅」「赤柔」「千春之印」「融斎」。</t>
         </is>
       </c>
       <c r="N299" t="inlineStr"/>
@@ -36067,7 +36075,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>請求記号: 呉 14|資料解説: 外題「原南陽墨竹」、本文「幽窓午睡足 捲簾日将曛 飽飯都無事 乗間画比君 戊寅早春 南陽老人併題」、 落款:「桂尌叢」「原昌克印」「柔子」 、外書に「呉氏郡山樓蔵」とあり。</t>
+          <t>請求記号: 呉 14|登録番号: M26325|資料解説: 外題「原南陽墨竹」、本文「幽窓午睡足 捲簾日将曛 飽飯都無事 乗間画比君 戊寅早春 南陽老人併題」、 落款:「桂尌叢」「原昌克印」「柔子」 、外書に「呉氏郡山樓蔵」とあり。</t>
         </is>
       </c>
       <c r="N300" t="inlineStr"/>
@@ -36185,7 +36193,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>請求記号: 呉 15|資料解説: 外題「吉益鄰斎易堂蔵」、本文「少年易老學難成 一寸光陰不可輕 未覺池塘春草夢 階前梧葉已秋聲 羸齋」 、落款「東洞季子」「辰之印」「子良」、 題箋に朱印「易堂」「九拾八(朱で八を七と修正)」とあり。</t>
+          <t>請求記号: 呉 15|登録番号: M26320|資料解説: 外題「吉益鄰斎易堂蔵」、本文「少年易老學難成 一寸光陰不可輕 未覺池塘春草夢 階前梧葉已秋聲 羸齋」 、落款「東洞季子」「辰之印」「子良」、 題箋に朱印「易堂」「九拾八(朱で八を七と修正)」とあり。</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -36311,7 +36319,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>請求記号: 呉 16|資料解説:中村佛庵書「毒鼓因縁」に三上章瑞,秦泰徳,谷其章,奈須恒徳,袁嘉裕,大倉八海,荻野八百吉の題言を付したもの。</t>
+          <t>請求記号: 呉 16|登録番号: M26318|資料解説:中村佛庵書「毒鼓因縁」に三上章瑞,秦泰徳,谷其章,奈須恒徳,袁嘉裕,大倉八海,荻野八百吉の題言を付したもの。</t>
         </is>
       </c>
       <c r="N302" t="inlineStr"/>
@@ -36907,7 +36915,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -37045,7 +37053,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -37183,7 +37191,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -37317,7 +37325,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -37451,7 +37459,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -37585,7 +37593,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -37719,7 +37727,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -37853,7 +37861,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -37987,7 +37995,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -38121,7 +38129,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -38255,7 +38263,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -38389,7 +38397,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -38523,7 +38531,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -38657,7 +38665,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -38791,7 +38799,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -38925,7 +38933,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -39059,7 +39067,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -39193,7 +39201,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -39327,7 +39335,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -39461,7 +39469,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -39595,7 +39603,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -39729,7 +39737,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -39863,7 +39871,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -39997,7 +40005,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -40131,7 +40139,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -40265,7 +40273,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -40403,7 +40411,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -40541,7 +40549,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -40679,7 +40687,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -40817,7 +40825,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -40947,7 +40955,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -41081,7 +41089,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -41215,7 +41223,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -41349,7 +41357,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -41483,7 +41491,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -41617,7 +41625,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -41751,7 +41759,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -41885,7 +41893,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -42019,7 +42027,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -42153,7 +42161,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -42287,7 +42295,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -42421,7 +42429,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -42555,7 +42563,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -42689,7 +42697,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -42819,7 +42827,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -42953,7 +42961,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -43083,7 +43091,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -43213,7 +43221,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -43343,7 +43351,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -43473,7 +43481,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -43607,7 +43615,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -43741,7 +43749,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -43875,7 +43883,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -44009,7 +44017,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -44143,7 +44151,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -44277,7 +44285,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -44411,7 +44419,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -44545,7 +44553,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -44679,7 +44687,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>古典籍コレクション[医学図書館]</t>
+          <t>古典籍コレクション [医学図書館]</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -28077,7 +28077,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>医聖堂前哲帖 22 [  栗本丹洲 ]</t>
+          <t>医聖堂前哲帖 22 作者不明</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -28098,14 +28098,10 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>[ 栗本丹洲 ]</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>くりもと たんしゅう|Kurimoto Tanshu</t>
-        </is>
-      </c>
+          <t>作者不明</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
@@ -28115,11 +28111,7 @@
           <t>26.7×20.4cm</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>江戸時代後期の医師、本草学者。幕府奥医師、4代目栗本瑞見。著作に「千虫譜」など。(1756-1834)</t>
-        </is>
-      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
@@ -30877,7 +30869,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>医聖堂前哲帖 46 作者不明</t>
+          <t>医聖堂前哲帖 46  [ 栗本丹洲 ]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -30898,10 +30890,14 @@
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>作者不明</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr"/>
+          <t>[ 栗本丹洲 ]</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>くりもと たんしゅう|Kurimoto Tanshu</t>
+        </is>
+      </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
@@ -30911,7 +30907,11 @@
           <t>23.4×20.6cm</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>江戸時代後期の医師、本草学者。幕府奥医師、4代目栗本瑞見。著作に「千虫譜」など。(1756-1834)</t>
+        </is>
+      </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr">

--- a/docs/collections/medlib/metadata/data.xlsx
+++ b/docs/collections/medlib/metadata/data.xlsx
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>撮影者不明|石坂秀哲</t>
+          <t>撮影者不明|石坂宗哲</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>解説: 掲載: 石坂秀哲の書(呉秀三藏)--『シーボルト先生 : 其生涯及功業』第二百五十一図|加工: マスキング(書の一部、2文字のみ囲み)|現秩序no.: 30|紙焼き記載no.: A45</t>
+          <t>解説: 掲載: 石坂宗哲の書(呉秀三藏)--『シーボルト先生 : 其生涯及功業』第二百五十一図|加工: マスキング(書の一部、2文字のみ囲み)|現秩序no.: 30|紙焼き記載no.: A45</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -14337,12 +14337,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>[ヴュルツブルクのシーボルト像建立記念写真]</t>
+          <t>[ヴュルツブルクのシーボルト像記念写真]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ヴュルツブルク ノ シーボルト ゾウ コンリュウ キネン シャシン|Vyurutsuburuku no shiboruto zo konryu kinen shashin</t>
+          <t>ヴュルツブルク ノ シーボルト ゾウ キネン シャシン|Vyurutsuburuku no shiboruto zo kinen shashin</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>解説: 現在、ヴュルツブルク大学と裁判所のあいだにあるシーボルト像の建立記念写真か(『シーボルト先生 : 其生涯及功業』p887-889による)|状態: 紙片張り付きのあと|現秩序no.: 103|紙焼き記載no.: B2</t>
+          <t>解説: ヴュルツブルク大学と裁判所のあいだにあるシーボルト像の写真。シーボルトの生誕を祝い1903年2月17日に撮影された。シーボルト像を挟んで左が長男アレクサーダー、右が次男ハインリヒ(小シーボルト)、右から4番目の人物は横手千代之助(東京帝国大学衛生学教授)(記事掲載: Feier des 109. Geburtstages Ph. Fr. v. Siebolds. "Ost-Asien” Mai 1903, Nr. 62, p.51 ) 『シーボルト先生 : 其生涯及功業』p887-889に像建立の経緯が掲載されている。|画像注記: 下部マスキングに隠れて"FRANKONIA-WÜRZUBURG”の記載あり。被写体の写真台紙のもの。|加工: マスキング|状態: 紙片張り付きのあと|現秩序no.: 103|紙焼き記載no.: B2</t>
         </is>
       </c>
       <c r="O115" t="inlineStr"/>
